--- a/Backlog - Tech Music.xlsx
+++ b/Backlog - Tech Music.xlsx
@@ -1,17 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="1037" documentId="11_7F4755BF84DCCE43E268565A8931F45BFA75341E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B76664C-29C9-406B-925A-01350AABF142}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\Downloads\documentary-repository\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{820D4768-24DC-4591-91EB-3EDF8EBD75A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Backlog" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Product Backlog'!$P$3:$P$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Product Backlog'!$P$3:$P$22</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -25,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -315,7 +318,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -417,45 +420,8 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </right>
       <top/>
       <bottom style="thin">
         <color theme="0" tint="-0.14999847407452621"/>
@@ -547,74 +513,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -624,7 +542,7 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -636,56 +554,91 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -774,7 +727,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="pt-BR"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -789,7 +742,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Product Backlog'!$AL$11</c:f>
+              <c:f>'Product Backlog'!$Y$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -810,9 +763,25 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="637CEF"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>'Product Backlog'!AK4:AK7</c:f>
+              <c:f>'Product Backlog'!$R$6:$R$9</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -832,7 +801,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Product Backlog'!$AL$12:$AL$15</c:f>
+              <c:f>'Product Backlog'!$Y$10:$Y$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -863,7 +832,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Product Backlog'!$AM$11</c:f>
+              <c:f>'Product Backlog'!$Z$9</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -884,9 +853,25 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:marker>
+              <c:symbol val="none"/>
+            </c:marker>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:ln w="28575" cap="rnd">
+                <a:solidFill>
+                  <a:srgbClr val="E3008C"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>'Product Backlog'!AK4:AK7</c:f>
+              <c:f>'Product Backlog'!$R$6:$R$9</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -906,7 +891,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Product Backlog'!$AM$12:$AM$15</c:f>
+              <c:f>'Product Backlog'!$Z$10:$Z$13</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -920,7 +905,7 @@
                   <c:v>113</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>113</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -985,7 +970,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="781953543"/>
@@ -1044,7 +1029,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="781917703"/>
@@ -1086,7 +1071,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="pt-BR"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -1116,7 +1101,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="pt-BR"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1673,16 +1658,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>656492</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>624254</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>49</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>46893</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>21248</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2030,1168 +2015,1243 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:AP42"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="B2:Z42"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="7.5703125" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
-    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="47.85546875" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.5703125" customWidth="1"/>
-    <col min="19" max="19" width="16.7109375" customWidth="1"/>
-    <col min="20" max="20" width="11.28515625" customWidth="1"/>
-    <col min="21" max="21" width="11.42578125" customWidth="1"/>
+    <col min="1" max="1" width="7.59765625" customWidth="1"/>
+    <col min="2" max="2" width="36.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.69921875" customWidth="1"/>
+    <col min="9" max="9" width="9.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="47.8984375" customWidth="1"/>
+    <col min="12" max="12" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.59765625" customWidth="1"/>
+    <col min="19" max="19" width="12.5" customWidth="1"/>
+    <col min="20" max="20" width="17.09765625" customWidth="1"/>
+    <col min="21" max="21" width="11.3984375" customWidth="1"/>
     <col min="22" max="22" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:42" ht="20.25" customHeight="1">
-      <c r="B2" s="47" t="s">
+    <row r="2" spans="2:26" ht="20.25" customHeight="1">
+      <c r="B2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="47"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="47"/>
-      <c r="AJ2" s="18"/>
-      <c r="AK2" s="18"/>
-      <c r="AL2" s="18"/>
-      <c r="AM2" s="18"/>
-      <c r="AN2" s="18"/>
-      <c r="AO2" s="18"/>
-    </row>
-    <row r="3" spans="2:42" ht="22.5" customHeight="1">
-      <c r="B3" s="48" t="s">
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
+    </row>
+    <row r="3" spans="2:26" ht="22.5" customHeight="1">
+      <c r="B3" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="27" t="s">
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="27" t="s">
+      <c r="M3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="27" t="s">
+      <c r="N3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="27" t="s">
+      <c r="O3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="P3" s="27" t="s">
+      <c r="P3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AJ3" s="18"/>
-      <c r="AK3" s="20" t="s">
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
+    </row>
+    <row r="4" spans="2:26" ht="34.5" customHeight="1">
+      <c r="B4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="15"/>
+      <c r="D4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" s="1">
+        <v>13</v>
+      </c>
+      <c r="O4" s="1">
+        <v>1</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="T4" s="29"/>
+      <c r="U4" s="29"/>
+      <c r="V4" s="29"/>
+      <c r="W4" s="29"/>
+      <c r="X4" s="29"/>
+      <c r="Y4" s="29"/>
+    </row>
+    <row r="5" spans="2:26" ht="30" customHeight="1">
+      <c r="B5" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N5" s="1">
+        <v>8</v>
+      </c>
+      <c r="O5" s="1">
+        <v>3</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q5" s="29"/>
+      <c r="R5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="AL3" s="32" t="s">
+      <c r="S5" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="AM3" s="33" t="s">
+      <c r="T5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="AN3" s="33" t="s">
+      <c r="U5" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="AO3" s="33" t="s">
+      <c r="V5" s="13" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="2:42" ht="34.5" customHeight="1">
-      <c r="B4" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="41"/>
-      <c r="D4" s="45" t="s">
+      <c r="W5" s="29"/>
+      <c r="X5" s="29"/>
+      <c r="Y5" s="29"/>
+    </row>
+    <row r="6" spans="2:26" ht="25.5" customHeight="1">
+      <c r="B6" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="20"/>
+      <c r="D6" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N6" s="6">
+        <v>8</v>
+      </c>
+      <c r="O6" s="6">
+        <v>2</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="S6" s="1">
+        <f>S7+S8+S9</f>
+        <v>215</v>
+      </c>
+      <c r="T6" s="2">
+        <v>215</v>
+      </c>
+      <c r="U6" s="1">
+        <f>U7+U8+U9</f>
+        <v>215</v>
+      </c>
+      <c r="V6" s="1">
+        <f>V9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:26" ht="32.25" customHeight="1">
+      <c r="B7" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7" s="1">
         <v>13</v>
       </c>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N4" s="2">
-        <v>13</v>
-      </c>
-      <c r="O4" s="2">
-        <v>1</v>
-      </c>
-      <c r="P4" s="2" t="s">
+      <c r="O7" s="1">
+        <v>2</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q7" s="29"/>
+      <c r="R7" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="AJ4" s="18"/>
-      <c r="AK4" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="AL4" s="2">
-        <f>AL5+AL6+AL7</f>
-        <v>215</v>
-      </c>
-      <c r="AM4" s="19">
-        <v>215</v>
-      </c>
-      <c r="AN4" s="2">
-        <f>AN5+AN6+AN7</f>
-        <v>102</v>
-      </c>
-      <c r="AO4" s="2">
-        <f>AO7</f>
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" spans="2:42" ht="30" customHeight="1">
-      <c r="B5" s="41" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N5" s="2">
-        <v>8</v>
-      </c>
-      <c r="O5" s="2">
-        <v>3</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="AJ5" s="18"/>
-      <c r="AK5" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="AL5" s="21">
+      <c r="S7" s="4">
         <f>N4+N5+N6+N14</f>
         <v>42</v>
       </c>
-      <c r="AM5" s="2">
+      <c r="T7" s="1">
         <v>42</v>
       </c>
-      <c r="AN5" s="2">
+      <c r="U7" s="1">
         <v>39</v>
       </c>
-      <c r="AO5" s="2">
-        <f>AM5-AN5</f>
+      <c r="V7" s="1">
+        <f>T7-U7</f>
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="2:42" ht="25.5" customHeight="1">
-      <c r="B6" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="50"/>
-      <c r="D6" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="N6" s="25">
-        <v>8</v>
-      </c>
-      <c r="O6" s="25">
-        <v>2</v>
-      </c>
-      <c r="P6" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="AJ6" s="18"/>
-      <c r="AK6" s="29" t="s">
+    <row r="8" spans="2:26" ht="31.5" customHeight="1">
+      <c r="B8" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="15"/>
+      <c r="D8" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N8" s="1">
+        <v>13</v>
+      </c>
+      <c r="O8" s="1">
+        <v>1</v>
+      </c>
+      <c r="P8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AL6" s="2">
+      <c r="Q8" s="29"/>
+      <c r="R8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="S8" s="1">
         <f>N7+N8+N9+N10+N12+N15+N19</f>
         <v>73</v>
       </c>
-      <c r="AM6" s="2">
-        <f>AL6+AO5</f>
+      <c r="T8" s="1">
+        <f>S8+V7</f>
         <v>76</v>
       </c>
-      <c r="AN6" s="2">
+      <c r="U8" s="1">
         <v>63</v>
       </c>
-      <c r="AO6" s="2">
-        <f>AM6-AN6</f>
+      <c r="V8" s="1">
+        <f>T8-U8</f>
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="2:42" ht="32.25" customHeight="1">
-      <c r="B7" s="49" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="45"/>
-      <c r="F7" s="45"/>
-      <c r="G7" s="45"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="45"/>
-      <c r="J7" s="45"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="2" t="s">
+    <row r="9" spans="2:26" ht="27.75" customHeight="1">
+      <c r="B9" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="15"/>
+      <c r="D9" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N7" s="2">
-        <v>13</v>
-      </c>
-      <c r="O7" s="2">
-        <v>2</v>
-      </c>
-      <c r="P7" s="2" t="s">
+      <c r="M9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" s="1">
+        <v>8</v>
+      </c>
+      <c r="O9" s="1">
+        <v>1</v>
+      </c>
+      <c r="P9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AJ7" s="18"/>
-      <c r="AK7" s="31" t="s">
+      <c r="Q9" s="29"/>
+      <c r="R9" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AL7" s="22">
+      <c r="S9" s="5">
         <f>N11+N13+N16+N17+N18+N20+N21+N22</f>
         <v>100</v>
       </c>
-      <c r="AM7" s="22">
-        <f>AL7+AO6</f>
+      <c r="T9" s="5">
+        <f>S9+V8</f>
         <v>113</v>
       </c>
-      <c r="AN7" s="22">
+      <c r="U9" s="5">
+        <v>113</v>
+      </c>
+      <c r="V9" s="5">
+        <f>T9-U9</f>
         <v>0</v>
       </c>
-      <c r="AO7" s="22">
-        <f>AM7-AN7</f>
+      <c r="Y9" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z9" s="12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="2:26" ht="33.75" customHeight="1">
+      <c r="B10" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N10" s="1">
+        <v>13</v>
+      </c>
+      <c r="O10" s="1">
+        <v>1</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q10" s="29"/>
+      <c r="R10" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="S10" s="1">
+        <v>0</v>
+      </c>
+      <c r="T10" s="1">
+        <v>0</v>
+      </c>
+      <c r="U10" s="1">
+        <v>0</v>
+      </c>
+      <c r="V10" s="1"/>
+      <c r="Y10" s="1">
+        <v>215</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="11" spans="2:26" ht="50.25" customHeight="1">
+      <c r="B11" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N11" s="1">
+        <v>21</v>
+      </c>
+      <c r="O11" s="1">
+        <v>2</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q11" s="29"/>
+      <c r="R11" s="29"/>
+      <c r="Y11" s="1">
+        <f>T6-T7</f>
+        <v>173</v>
+      </c>
+      <c r="Z11" s="1">
+        <f>T6-U7</f>
+        <v>176</v>
+      </c>
+    </row>
+    <row r="12" spans="2:26" ht="39.75" customHeight="1">
+      <c r="B12" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="K12" s="17"/>
+      <c r="L12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N12" s="1">
+        <v>5</v>
+      </c>
+      <c r="O12" s="1">
+        <v>2</v>
+      </c>
+      <c r="P12" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q12" s="29"/>
+      <c r="R12" s="29"/>
+      <c r="S12" s="29"/>
+      <c r="T12" s="29"/>
+      <c r="U12" s="29"/>
+      <c r="V12" s="29"/>
+      <c r="W12" s="29"/>
+      <c r="X12" s="29"/>
+      <c r="Y12" s="1">
+        <f>Y11-(T8-V7)</f>
+        <v>100</v>
+      </c>
+      <c r="Z12" s="1">
+        <f>Z11-U8</f>
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="2:42" ht="31.5" customHeight="1">
-      <c r="B8" s="41" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="45" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="45"/>
-      <c r="K8" s="45"/>
-      <c r="L8" s="2" t="s">
+    <row r="13" spans="2:26" ht="29.25" customHeight="1">
+      <c r="B13" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N13" s="6">
+        <v>8</v>
+      </c>
+      <c r="O13" s="6">
+        <v>3</v>
+      </c>
+      <c r="P13" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q13" s="29"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="31"/>
+      <c r="T13" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="U13" s="33"/>
+      <c r="V13" s="34"/>
+      <c r="W13" s="31"/>
+      <c r="X13" s="35"/>
+      <c r="Y13" s="1">
+        <f>Y12-(T9-V8)</f>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="1">
+        <f>Z12-U9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:26" ht="29.25" customHeight="1">
+      <c r="B14" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="M14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N8" s="2">
+      <c r="N14" s="1">
         <v>13</v>
       </c>
-      <c r="O8" s="2">
+      <c r="O14" s="1">
         <v>1</v>
       </c>
-      <c r="P8" s="2" t="s">
+      <c r="P14" s="30" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q14" s="29"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="36"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="36"/>
+      <c r="W14" s="31"/>
+      <c r="X14" s="34"/>
+      <c r="Y14" s="29"/>
+      <c r="Z14" s="29"/>
+    </row>
+    <row r="15" spans="2:26" ht="36" customHeight="1">
+      <c r="B15" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="N15" s="6">
+        <v>13</v>
+      </c>
+      <c r="O15" s="6">
+        <v>2</v>
+      </c>
+      <c r="P15" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="AJ8" s="18"/>
-      <c r="AK8" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="AL8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AM8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN8" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO8" s="2"/>
-    </row>
-    <row r="9" spans="2:42" ht="27.75" customHeight="1">
-      <c r="B9" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="45" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="45"/>
-      <c r="L9" s="2" t="s">
+      <c r="Q15" s="29"/>
+      <c r="R15" s="29"/>
+      <c r="S15" s="37"/>
+      <c r="T15" s="29"/>
+      <c r="U15" s="29"/>
+      <c r="V15" s="38"/>
+      <c r="W15" s="39"/>
+      <c r="X15" s="29"/>
+      <c r="Y15" s="29"/>
+      <c r="Z15" s="29"/>
+    </row>
+    <row r="16" spans="2:26" ht="36.75" customHeight="1">
+      <c r="B16" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="14"/>
+      <c r="D16" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="N16" s="6">
+        <v>21</v>
+      </c>
+      <c r="O16" s="6">
+        <v>2</v>
+      </c>
+      <c r="P16" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q16" s="29"/>
+      <c r="R16" s="29"/>
+      <c r="S16" s="40"/>
+      <c r="T16" s="29"/>
+      <c r="U16" s="29"/>
+      <c r="V16" s="41"/>
+      <c r="W16" s="42"/>
+      <c r="X16" s="35"/>
+      <c r="Y16" s="29"/>
+      <c r="Z16" s="29"/>
+    </row>
+    <row r="17" spans="2:26" ht="34.5" customHeight="1">
+      <c r="B17" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N17" s="6">
+        <v>8</v>
+      </c>
+      <c r="O17" s="6">
+        <v>3</v>
+      </c>
+      <c r="P17" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q17" s="29"/>
+      <c r="R17" s="29"/>
+      <c r="S17" s="43"/>
+      <c r="T17" s="29"/>
+      <c r="U17" s="29"/>
+      <c r="V17" s="44"/>
+      <c r="W17" s="45"/>
+      <c r="X17" s="34"/>
+      <c r="Y17" s="29"/>
+      <c r="Z17" s="29"/>
+    </row>
+    <row r="18" spans="2:26" ht="27.75" customHeight="1">
+      <c r="B18" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="N18" s="1">
+        <v>13</v>
+      </c>
+      <c r="O18" s="1">
+        <v>2</v>
+      </c>
+      <c r="P18" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q18" s="29"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="43"/>
+      <c r="T18" s="29"/>
+      <c r="U18" s="29"/>
+      <c r="V18" s="44"/>
+      <c r="W18" s="45"/>
+      <c r="X18" s="34"/>
+      <c r="Y18" s="29"/>
+      <c r="Z18" s="29"/>
+    </row>
+    <row r="19" spans="2:26" ht="30" customHeight="1">
+      <c r="B19" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="M19" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N19" s="1">
         <v>8</v>
       </c>
-      <c r="O9" s="2">
+      <c r="O19" s="8">
         <v>1</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="P19" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="AJ9" s="18"/>
-      <c r="AK9" s="18"/>
-      <c r="AL9" s="18"/>
-      <c r="AM9" s="18"/>
-      <c r="AN9" s="18"/>
-      <c r="AO9" s="18"/>
-    </row>
-    <row r="10" spans="2:42" ht="33.75" customHeight="1">
-      <c r="B10" s="49" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="49"/>
-      <c r="D10" s="45" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="45"/>
-      <c r="I10" s="45"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="45"/>
-      <c r="L10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M10" s="2" t="s">
+      <c r="Q19" s="29"/>
+      <c r="R19" s="29"/>
+      <c r="S19" s="29"/>
+      <c r="T19" s="29"/>
+      <c r="U19" s="29"/>
+      <c r="V19" s="29"/>
+      <c r="W19" s="29"/>
+      <c r="X19" s="29"/>
+      <c r="Y19" s="29"/>
+      <c r="Z19" s="29"/>
+    </row>
+    <row r="20" spans="2:26" ht="24" customHeight="1">
+      <c r="B20" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N20" s="1">
+        <v>8</v>
+      </c>
+      <c r="O20" s="1">
+        <v>3</v>
+      </c>
+      <c r="P20" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q20" s="29"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="29"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="29"/>
+      <c r="W20" s="29"/>
+      <c r="X20" s="29"/>
+      <c r="Y20" s="29"/>
+      <c r="Z20" s="29"/>
+    </row>
+    <row r="21" spans="2:26" ht="27" customHeight="1">
+      <c r="B21" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="20"/>
+      <c r="D21" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N21" s="6">
+        <v>8</v>
+      </c>
+      <c r="O21" s="6">
+        <v>2</v>
+      </c>
+      <c r="P21" s="30" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q21" s="29"/>
+      <c r="R21" s="29"/>
+      <c r="S21" s="29"/>
+      <c r="T21" s="29"/>
+      <c r="U21" s="29"/>
+      <c r="V21" s="29"/>
+      <c r="W21" s="29"/>
+      <c r="X21" s="29"/>
+      <c r="Y21" s="29"/>
+      <c r="Z21" s="29"/>
+    </row>
+    <row r="22" spans="2:26" ht="32.25" customHeight="1">
+      <c r="B22" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="15"/>
+      <c r="D22" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="M22" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N22" s="6">
         <v>13</v>
       </c>
-      <c r="O10" s="2">
-        <v>1</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ10" s="18"/>
-      <c r="AK10" s="23"/>
-      <c r="AL10" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM10" s="44"/>
-      <c r="AN10" s="24"/>
-      <c r="AO10" s="23"/>
-      <c r="AP10" s="8"/>
-    </row>
-    <row r="11" spans="2:42" ht="50.25" customHeight="1">
-      <c r="B11" s="41" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="45" t="s">
-        <v>38</v>
-      </c>
-      <c r="E11" s="45"/>
-      <c r="F11" s="45"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="45"/>
-      <c r="I11" s="45"/>
-      <c r="J11" s="45"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N11" s="2">
-        <v>21</v>
-      </c>
-      <c r="O11" s="2">
-        <v>2</v>
-      </c>
-      <c r="P11" s="2" t="s">
+      <c r="O22" s="6">
+        <v>3</v>
+      </c>
+      <c r="P22" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="AJ11" s="18"/>
-      <c r="AK11" s="16"/>
-      <c r="AL11" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="AM11" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="AN11" s="16"/>
-      <c r="AO11" s="23"/>
-      <c r="AP11" s="14"/>
-    </row>
-    <row r="12" spans="2:42" ht="39.75" customHeight="1">
-      <c r="B12" s="49" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="49"/>
-      <c r="D12" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="45"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N12" s="2">
-        <v>5</v>
-      </c>
-      <c r="O12" s="2">
-        <v>2</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ12" s="18"/>
-      <c r="AK12" s="17"/>
-      <c r="AL12" s="2">
-        <v>215</v>
-      </c>
-      <c r="AM12" s="2">
-        <v>215</v>
-      </c>
-      <c r="AN12" s="1"/>
-      <c r="AO12" s="15"/>
-    </row>
-    <row r="13" spans="2:42" ht="29.25" customHeight="1">
-      <c r="B13" s="41" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="41"/>
-      <c r="D13" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="42"/>
-      <c r="K13" s="42"/>
-      <c r="L13" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="M13" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="N13" s="25">
-        <v>8</v>
-      </c>
-      <c r="O13" s="25">
-        <v>3</v>
-      </c>
-      <c r="P13" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="AJ13" s="18"/>
-      <c r="AK13" s="7"/>
-      <c r="AL13" s="2">
-        <f>AM4-AM5</f>
-        <v>173</v>
-      </c>
-      <c r="AM13" s="2">
-        <f>AM4-AN5</f>
-        <v>176</v>
-      </c>
-      <c r="AN13" s="5"/>
-      <c r="AO13" s="6"/>
-      <c r="AP13" s="8"/>
-    </row>
-    <row r="14" spans="2:42" ht="29.25" customHeight="1">
-      <c r="B14" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="26"/>
-      <c r="D14" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="42"/>
-      <c r="L14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N14" s="2">
-        <v>13</v>
-      </c>
-      <c r="O14" s="2">
-        <v>1</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="AJ14" s="18"/>
-      <c r="AK14" s="13"/>
-      <c r="AL14" s="2">
-        <f>AL13-(AM6-AO5)</f>
-        <v>100</v>
-      </c>
-      <c r="AM14" s="2">
-        <f>AM13-AN6</f>
-        <v>113</v>
-      </c>
-      <c r="AN14" s="10"/>
-      <c r="AO14" s="4"/>
-      <c r="AP14" s="14"/>
-    </row>
-    <row r="15" spans="2:42" ht="36" customHeight="1">
-      <c r="B15" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
-      <c r="J15" s="42"/>
-      <c r="K15" s="42"/>
-      <c r="L15" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="M15" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="N15" s="25">
-        <v>13</v>
-      </c>
-      <c r="O15" s="25">
-        <v>2</v>
-      </c>
-      <c r="P15" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ15" s="18"/>
-      <c r="AK15" s="13"/>
-      <c r="AL15" s="2">
-        <f>AL14-(AM7-AO6)</f>
-        <v>0</v>
-      </c>
-      <c r="AM15" s="2">
-        <f>AM14-AN7</f>
-        <v>113</v>
-      </c>
-      <c r="AN15" s="10"/>
-      <c r="AO15" s="4"/>
-      <c r="AP15" s="14"/>
-    </row>
-    <row r="16" spans="2:42" ht="36.75" customHeight="1">
-      <c r="B16" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="26"/>
-      <c r="D16" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42"/>
-      <c r="J16" s="42"/>
-      <c r="K16" s="42"/>
-      <c r="L16" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="M16" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="N16" s="25">
-        <v>21</v>
-      </c>
-      <c r="O16" s="25">
-        <v>2</v>
-      </c>
-      <c r="P16" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q16" s="18"/>
-      <c r="R16" s="13"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="3"/>
-      <c r="U16" s="10"/>
-      <c r="V16" s="4"/>
-      <c r="W16" s="24"/>
-      <c r="X16" s="18"/>
-    </row>
-    <row r="17" spans="2:24" ht="34.5" customHeight="1">
-      <c r="B17" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="26"/>
-      <c r="D17" s="45" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
-      <c r="L17" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="M17" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="N17" s="25">
-        <v>8</v>
-      </c>
-      <c r="O17" s="25">
-        <v>3</v>
-      </c>
-      <c r="P17" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q17" s="18"/>
-      <c r="R17" s="9"/>
-      <c r="S17" s="10"/>
-      <c r="T17" s="13"/>
-      <c r="U17" s="13"/>
-      <c r="V17" s="4"/>
-      <c r="W17" s="24"/>
-      <c r="X17" s="18"/>
-    </row>
-    <row r="18" spans="2:24" ht="27.75" customHeight="1">
-      <c r="B18" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="26"/>
-      <c r="D18" s="46" t="s">
-        <v>54</v>
-      </c>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="46"/>
-      <c r="L18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N18" s="2">
-        <v>13</v>
-      </c>
-      <c r="O18" s="2">
-        <v>2</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q18" s="18"/>
-      <c r="R18" s="9"/>
-      <c r="S18" s="10"/>
-      <c r="T18" s="4"/>
-      <c r="U18" s="11"/>
-      <c r="V18" s="12"/>
-      <c r="W18" s="18"/>
-      <c r="X18" s="18"/>
-    </row>
-    <row r="19" spans="2:24" ht="30" customHeight="1">
-      <c r="B19" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N19" s="2">
-        <v>8</v>
-      </c>
-      <c r="O19" s="28">
-        <v>1</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q19" s="18"/>
-      <c r="R19" s="18"/>
-      <c r="S19" s="18"/>
-      <c r="T19" s="18"/>
-      <c r="U19" s="18"/>
-      <c r="V19" s="18"/>
-      <c r="W19" s="18"/>
-      <c r="X19" s="18"/>
-    </row>
-    <row r="20" spans="2:24" ht="24" customHeight="1">
-      <c r="B20" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="26"/>
-      <c r="D20" s="42" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="42"/>
-      <c r="K20" s="42"/>
-      <c r="L20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N20" s="2">
-        <v>8</v>
-      </c>
-      <c r="O20" s="2">
-        <v>3</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q20" s="18"/>
-      <c r="R20" s="18"/>
-      <c r="S20" s="18"/>
-      <c r="T20" s="18"/>
-      <c r="U20" s="18"/>
-      <c r="V20" s="18"/>
-      <c r="W20" s="18"/>
-      <c r="X20" s="18"/>
-    </row>
-    <row r="21" spans="2:24" ht="27" customHeight="1">
-      <c r="B21" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="40"/>
-      <c r="D21" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="42"/>
-      <c r="J21" s="42"/>
-      <c r="K21" s="42"/>
-      <c r="L21" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="M21" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="N21" s="25">
-        <v>8</v>
-      </c>
-      <c r="O21" s="25">
-        <v>2</v>
-      </c>
-      <c r="P21" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q21" s="18"/>
-      <c r="R21" s="18"/>
-      <c r="S21" s="18"/>
-      <c r="T21" s="18"/>
-      <c r="U21" s="18"/>
-      <c r="V21" s="18"/>
-      <c r="W21" s="18"/>
-      <c r="X21" s="18"/>
-    </row>
-    <row r="22" spans="2:24" ht="32.25" customHeight="1">
-      <c r="B22" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="39" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="M22" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="N22" s="25">
-        <v>13</v>
-      </c>
-      <c r="O22" s="25">
-        <v>3</v>
-      </c>
-      <c r="P22" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q22" s="18"/>
-      <c r="R22" s="18"/>
-      <c r="S22" s="18"/>
-      <c r="T22" s="18"/>
-      <c r="U22" s="18"/>
-      <c r="V22" s="18"/>
-      <c r="W22" s="18"/>
-      <c r="X22" s="18"/>
-    </row>
-    <row r="24" spans="2:24">
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-    </row>
-    <row r="25" spans="2:24">
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="38"/>
-    </row>
-    <row r="26" spans="2:24">
-      <c r="D26" s="38"/>
-      <c r="E26" s="38"/>
-      <c r="F26" s="38"/>
-      <c r="G26" s="38"/>
-      <c r="H26" s="38"/>
-      <c r="I26" s="38"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="38"/>
-    </row>
-    <row r="27" spans="2:24">
-      <c r="D27" s="38"/>
-      <c r="E27" s="38"/>
-      <c r="F27" s="38"/>
-      <c r="G27" s="38"/>
-      <c r="H27" s="38"/>
-      <c r="I27" s="38"/>
-      <c r="J27" s="38"/>
-      <c r="K27" s="38"/>
-    </row>
-    <row r="28" spans="2:24">
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="38"/>
-      <c r="J28" s="38"/>
-      <c r="K28" s="38"/>
-    </row>
-    <row r="29" spans="2:24">
-      <c r="B29" s="34"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="38"/>
-      <c r="F29" s="38"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="38"/>
-      <c r="I29" s="38"/>
-      <c r="J29" s="38"/>
-      <c r="K29" s="38"/>
-    </row>
-    <row r="30" spans="2:24">
-      <c r="D30" s="38"/>
-      <c r="E30" s="38"/>
-      <c r="F30" s="38"/>
-      <c r="G30" s="38"/>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
-      <c r="J30" s="38"/>
-      <c r="K30" s="38"/>
-    </row>
-    <row r="31" spans="2:24" ht="32.25" customHeight="1">
-      <c r="B31" s="34"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="36"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="36"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
-      <c r="J31" s="36"/>
-      <c r="K31" s="36"/>
-    </row>
-    <row r="32" spans="2:24" ht="44.25" customHeight="1">
-      <c r="B32" s="34"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="36"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="36"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="36"/>
-      <c r="K32" s="36"/>
+      <c r="Q22" s="29"/>
+      <c r="R22" s="29"/>
+      <c r="S22" s="29"/>
+      <c r="T22" s="29"/>
+      <c r="U22" s="29"/>
+      <c r="V22" s="29"/>
+      <c r="W22" s="29"/>
+      <c r="X22" s="29"/>
+      <c r="Y22" s="29"/>
+      <c r="Z22" s="29"/>
+    </row>
+    <row r="23" spans="2:26">
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="29"/>
+      <c r="T23" s="29"/>
+      <c r="U23" s="29"/>
+      <c r="V23" s="29"/>
+      <c r="W23" s="29"/>
+      <c r="X23" s="29"/>
+      <c r="Y23" s="29"/>
+      <c r="Z23" s="29"/>
+    </row>
+    <row r="24" spans="2:26">
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="P24" s="29"/>
+      <c r="Q24" s="29"/>
+      <c r="R24" s="29"/>
+      <c r="S24" s="29"/>
+      <c r="T24" s="29"/>
+      <c r="U24" s="29"/>
+      <c r="V24" s="29"/>
+      <c r="W24" s="29"/>
+      <c r="X24" s="29"/>
+      <c r="Y24" s="29"/>
+      <c r="Z24" s="29"/>
+    </row>
+    <row r="25" spans="2:26">
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="P25" s="29"/>
+      <c r="Q25" s="29"/>
+      <c r="R25" s="29"/>
+      <c r="S25" s="29"/>
+      <c r="T25" s="29"/>
+      <c r="U25" s="29"/>
+      <c r="V25" s="29"/>
+      <c r="W25" s="29"/>
+      <c r="X25" s="29"/>
+      <c r="Y25" s="29"/>
+      <c r="Z25" s="29"/>
+    </row>
+    <row r="26" spans="2:26">
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="25"/>
+      <c r="K26" s="25"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="29"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="29"/>
+      <c r="T26" s="29"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="29"/>
+      <c r="W26" s="29"/>
+      <c r="X26" s="29"/>
+      <c r="Y26" s="29"/>
+      <c r="Z26" s="29"/>
+    </row>
+    <row r="27" spans="2:26">
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="29"/>
+      <c r="R27" s="29"/>
+      <c r="S27" s="29"/>
+      <c r="T27" s="29"/>
+      <c r="U27" s="29"/>
+      <c r="V27" s="29"/>
+      <c r="W27" s="29"/>
+      <c r="X27" s="29"/>
+      <c r="Y27" s="29"/>
+      <c r="Z27" s="29"/>
+    </row>
+    <row r="28" spans="2:26">
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="P28" s="29"/>
+      <c r="Q28" s="29"/>
+      <c r="R28" s="29"/>
+      <c r="S28" s="29"/>
+      <c r="T28" s="29"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="29"/>
+      <c r="W28" s="29"/>
+      <c r="X28" s="29"/>
+      <c r="Y28" s="29"/>
+      <c r="Z28" s="29"/>
+    </row>
+    <row r="29" spans="2:26">
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="29"/>
+      <c r="W29" s="29"/>
+      <c r="X29" s="29"/>
+      <c r="Y29" s="29"/>
+      <c r="Z29" s="29"/>
+    </row>
+    <row r="30" spans="2:26">
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="P30" s="29"/>
+      <c r="Q30" s="29"/>
+      <c r="R30" s="29"/>
+      <c r="S30" s="29"/>
+      <c r="T30" s="29"/>
+      <c r="U30" s="29"/>
+      <c r="V30" s="29"/>
+      <c r="W30" s="29"/>
+      <c r="X30" s="29"/>
+      <c r="Y30" s="29"/>
+      <c r="Z30" s="29"/>
+    </row>
+    <row r="31" spans="2:26" ht="32.25" customHeight="1">
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="26"/>
+      <c r="K31" s="26"/>
+    </row>
+    <row r="32" spans="2:26" ht="44.25" customHeight="1">
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="26"/>
+      <c r="K32" s="26"/>
     </row>
     <row r="33" spans="2:11" ht="48" customHeight="1">
-      <c r="B33" s="34"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="36"/>
-      <c r="K33" s="36"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="26"/>
     </row>
     <row r="34" spans="2:11" ht="66.75" customHeight="1">
-      <c r="B34" s="34"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="26"/>
+      <c r="K34" s="26"/>
     </row>
     <row r="35" spans="2:11" ht="60" customHeight="1">
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="36"/>
-      <c r="E35" s="36"/>
-      <c r="F35" s="36"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="36"/>
-      <c r="I35" s="36"/>
-      <c r="J35" s="36"/>
-      <c r="K35" s="36"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="26"/>
+      <c r="K35" s="26"/>
     </row>
     <row r="36" spans="2:11" ht="37.5" customHeight="1">
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="36"/>
-      <c r="E36" s="36"/>
-      <c r="F36" s="36"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="36"/>
-      <c r="I36" s="36"/>
-      <c r="J36" s="36"/>
-      <c r="K36" s="36"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="26"/>
     </row>
     <row r="37" spans="2:11" ht="36" customHeight="1">
-      <c r="B37" s="34"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="36"/>
-      <c r="E37" s="36"/>
-      <c r="F37" s="36"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="36"/>
-      <c r="I37" s="36"/>
-      <c r="J37" s="36"/>
-      <c r="K37" s="36"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
+      <c r="K37" s="26"/>
     </row>
     <row r="38" spans="2:11" ht="39" customHeight="1">
-      <c r="B38" s="37"/>
-      <c r="C38" s="37"/>
-      <c r="D38" s="36"/>
-      <c r="E38" s="36"/>
-      <c r="F38" s="36"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="36"/>
-      <c r="I38" s="36"/>
-      <c r="J38" s="36"/>
-      <c r="K38" s="36"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="26"/>
+      <c r="J38" s="26"/>
+      <c r="K38" s="26"/>
     </row>
     <row r="39" spans="2:11" ht="19.5" customHeight="1">
-      <c r="B39" s="34"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="36"/>
-      <c r="F39" s="36"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="36"/>
-      <c r="I39" s="36"/>
-      <c r="J39" s="36"/>
-      <c r="K39" s="36"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="26"/>
+      <c r="K39" s="26"/>
     </row>
     <row r="40" spans="2:11">
-      <c r="B40" s="34"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="36"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
-      <c r="J40" s="36"/>
-      <c r="K40" s="36"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="26"/>
+      <c r="K40" s="26"/>
     </row>
     <row r="41" spans="2:11">
-      <c r="B41" s="34"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="36"/>
-      <c r="G41" s="36"/>
-      <c r="H41" s="36"/>
-      <c r="I41" s="36"/>
-      <c r="J41" s="36"/>
-      <c r="K41" s="36"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
+      <c r="K41" s="26"/>
     </row>
     <row r="42" spans="2:11">
-      <c r="B42" s="34"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="35"/>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="36"/>
-      <c r="I42" s="36"/>
-      <c r="J42" s="36"/>
-      <c r="K42" s="36"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
     </row>
   </sheetData>
   <autoFilter ref="P3:P22" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <mergeCells count="67">
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:K12"/>
-    <mergeCell ref="D11:K11"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D9:K9"/>
-    <mergeCell ref="D10:K10"/>
-    <mergeCell ref="B2:P2"/>
-    <mergeCell ref="D4:K4"/>
-    <mergeCell ref="D5:K5"/>
-    <mergeCell ref="D7:K7"/>
-    <mergeCell ref="D8:K8"/>
-    <mergeCell ref="D3:K3"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:K6"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D15:K15"/>
-    <mergeCell ref="AL10:AM10"/>
-    <mergeCell ref="D14:K14"/>
-    <mergeCell ref="D16:K16"/>
-    <mergeCell ref="D17:K17"/>
-    <mergeCell ref="D18:K18"/>
-    <mergeCell ref="D13:K13"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D19:K19"/>
-    <mergeCell ref="D20:K20"/>
-    <mergeCell ref="D21:K21"/>
-    <mergeCell ref="D28:K28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:K29"/>
-    <mergeCell ref="D30:K30"/>
-    <mergeCell ref="D31:K31"/>
-    <mergeCell ref="D22:K22"/>
-    <mergeCell ref="D24:K24"/>
-    <mergeCell ref="D25:K25"/>
-    <mergeCell ref="D26:K26"/>
-    <mergeCell ref="D27:K27"/>
+  <mergeCells count="66">
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D40:K40"/>
+    <mergeCell ref="D41:K41"/>
+    <mergeCell ref="D42:K42"/>
     <mergeCell ref="D36:K36"/>
     <mergeCell ref="D37:K37"/>
     <mergeCell ref="D38:K38"/>
@@ -3207,13 +3267,50 @@
     <mergeCell ref="D35:K35"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="D40:K40"/>
-    <mergeCell ref="D41:K41"/>
-    <mergeCell ref="D42:K42"/>
+    <mergeCell ref="D29:K29"/>
+    <mergeCell ref="D30:K30"/>
+    <mergeCell ref="D31:K31"/>
+    <mergeCell ref="D22:K22"/>
+    <mergeCell ref="D24:K24"/>
+    <mergeCell ref="D25:K25"/>
+    <mergeCell ref="D26:K26"/>
+    <mergeCell ref="D27:K27"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D15:K15"/>
+    <mergeCell ref="D14:K14"/>
+    <mergeCell ref="D16:K16"/>
+    <mergeCell ref="D17:K17"/>
+    <mergeCell ref="D18:K18"/>
+    <mergeCell ref="D13:K13"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D19:K19"/>
+    <mergeCell ref="D20:K20"/>
+    <mergeCell ref="D21:K21"/>
+    <mergeCell ref="D28:K28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="D4:K4"/>
+    <mergeCell ref="D5:K5"/>
+    <mergeCell ref="D7:K7"/>
+    <mergeCell ref="D8:K8"/>
+    <mergeCell ref="D3:K3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:K6"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:K12"/>
+    <mergeCell ref="D11:K11"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D9:K9"/>
+    <mergeCell ref="D10:K10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
